--- a/DesignerConfigs/Datas/MoneyInterval.xlsx
+++ b/DesignerConfigs/Datas/MoneyInterval.xlsx
@@ -742,7 +742,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -751,9 +751,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="22" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1445,31 +1442,31 @@
         <v>0</v>
       </c>
       <c r="C6" s="1">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="D6" s="1">
         <v>300</v>
       </c>
-      <c r="E6" s="3">
-        <v>25</v>
-      </c>
-      <c r="F6" s="3">
-        <v>35</v>
-      </c>
-      <c r="G6" s="3">
-        <v>25</v>
-      </c>
-      <c r="H6" s="3">
-        <v>35</v>
-      </c>
-      <c r="I6" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="J6" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="K6" s="3">
-        <v>8</v>
+      <c r="E6" s="1">
+        <v>13.3</v>
+      </c>
+      <c r="F6" s="1">
+        <v>17.9</v>
+      </c>
+      <c r="G6" s="1">
+        <v>13.3</v>
+      </c>
+      <c r="H6" s="1">
+        <v>17.9</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1">
+        <v>2.5</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1477,22 +1474,22 @@
         <v>1</v>
       </c>
       <c r="C7" s="1">
-        <v>270</v>
+        <v>210</v>
       </c>
       <c r="D7" s="1">
-        <v>300</v>
-      </c>
-      <c r="E7" s="3">
-        <v>12</v>
-      </c>
-      <c r="F7" s="3">
-        <v>18</v>
-      </c>
-      <c r="G7" s="3">
-        <v>12</v>
-      </c>
-      <c r="H7" s="3">
-        <v>18</v>
+        <v>240</v>
+      </c>
+      <c r="E7" s="1">
+        <v>9</v>
+      </c>
+      <c r="F7" s="1">
+        <v>12.2</v>
+      </c>
+      <c r="G7" s="1">
+        <v>9</v>
+      </c>
+      <c r="H7" s="1">
+        <v>12.2</v>
       </c>
       <c r="I7" s="1">
         <v>0</v>
@@ -1500,8 +1497,8 @@
       <c r="J7" s="1">
         <v>0</v>
       </c>
-      <c r="K7" s="3">
-        <v>8</v>
+      <c r="K7" s="1">
+        <v>1.84</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1509,22 +1506,22 @@
         <v>2</v>
       </c>
       <c r="C8" s="1">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="D8" s="1">
-        <v>270</v>
-      </c>
-      <c r="E8" s="3">
-        <v>11</v>
-      </c>
-      <c r="F8" s="3">
-        <v>16.5</v>
-      </c>
-      <c r="G8" s="3">
-        <v>11</v>
-      </c>
-      <c r="H8" s="3">
-        <v>16.5</v>
+        <v>210</v>
+      </c>
+      <c r="E8" s="1">
+        <v>7.2</v>
+      </c>
+      <c r="F8" s="1">
+        <v>9.8</v>
+      </c>
+      <c r="G8" s="1">
+        <v>7.2</v>
+      </c>
+      <c r="H8" s="1">
+        <v>9.8</v>
       </c>
       <c r="I8" s="1">
         <v>0</v>
@@ -1532,8 +1529,8 @@
       <c r="J8" s="1">
         <v>0</v>
       </c>
-      <c r="K8" s="3">
-        <v>7.2</v>
+      <c r="K8" s="1">
+        <v>1.55</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1541,22 +1538,22 @@
         <v>3</v>
       </c>
       <c r="C9" s="1">
-        <v>210</v>
+        <v>158</v>
       </c>
       <c r="D9" s="1">
-        <v>240</v>
-      </c>
-      <c r="E9" s="3">
-        <v>10</v>
-      </c>
-      <c r="F9" s="3">
-        <v>15</v>
-      </c>
-      <c r="G9" s="3">
-        <v>10</v>
-      </c>
-      <c r="H9" s="3">
-        <v>15</v>
+        <v>180</v>
+      </c>
+      <c r="E9" s="1">
+        <v>5.6</v>
+      </c>
+      <c r="F9" s="1">
+        <v>7.6</v>
+      </c>
+      <c r="G9" s="1">
+        <v>5.6</v>
+      </c>
+      <c r="H9" s="1">
+        <v>7.6</v>
       </c>
       <c r="I9" s="1">
         <v>0</v>
@@ -1564,8 +1561,8 @@
       <c r="J9" s="1">
         <v>0</v>
       </c>
-      <c r="K9" s="3">
-        <v>6.5</v>
+      <c r="K9" s="1">
+        <v>1.3</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1573,22 +1570,22 @@
         <v>4</v>
       </c>
       <c r="C10" s="1">
-        <v>180</v>
+        <v>135</v>
       </c>
       <c r="D10" s="1">
-        <v>210</v>
-      </c>
-      <c r="E10" s="3">
-        <v>8</v>
-      </c>
-      <c r="F10" s="3">
-        <v>12</v>
-      </c>
-      <c r="G10" s="3">
-        <v>8</v>
-      </c>
-      <c r="H10" s="3">
-        <v>12</v>
+        <v>158</v>
+      </c>
+      <c r="E10" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="F10" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="G10" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="H10" s="1">
+        <v>6.1</v>
       </c>
       <c r="I10" s="1">
         <v>0</v>
@@ -1596,8 +1593,8 @@
       <c r="J10" s="1">
         <v>0</v>
       </c>
-      <c r="K10" s="3">
-        <v>5.2</v>
+      <c r="K10" s="1">
+        <v>1.13</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1605,22 +1602,22 @@
         <v>5</v>
       </c>
       <c r="C11" s="1">
-        <v>160</v>
+        <v>113</v>
       </c>
       <c r="D11" s="1">
-        <v>180</v>
-      </c>
-      <c r="E11" s="3">
-        <v>4</v>
-      </c>
-      <c r="F11" s="3">
-        <v>6</v>
-      </c>
-      <c r="G11" s="3">
-        <v>4</v>
-      </c>
-      <c r="H11" s="3">
-        <v>6</v>
+        <v>135</v>
+      </c>
+      <c r="E11" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="F11" s="1">
+        <v>4.8</v>
+      </c>
+      <c r="G11" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="H11" s="1">
+        <v>4.8</v>
       </c>
       <c r="I11" s="1">
         <v>0</v>
@@ -1628,8 +1625,8 @@
       <c r="J11" s="1">
         <v>0</v>
       </c>
-      <c r="K11" s="3">
-        <v>2.5</v>
+      <c r="K11" s="1">
+        <v>0.98</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1637,22 +1634,22 @@
         <v>6</v>
       </c>
       <c r="C12" s="1">
-        <v>140</v>
+        <v>94</v>
       </c>
       <c r="D12" s="1">
-        <v>160</v>
-      </c>
-      <c r="E12" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="F12" s="3">
-        <v>2.25</v>
-      </c>
-      <c r="G12" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="H12" s="3">
-        <v>2.25</v>
+        <v>113</v>
+      </c>
+      <c r="E12" s="1">
+        <v>2.7</v>
+      </c>
+      <c r="F12" s="1">
+        <v>3.7</v>
+      </c>
+      <c r="G12" s="1">
+        <v>2.7</v>
+      </c>
+      <c r="H12" s="1">
+        <v>3.7</v>
       </c>
       <c r="I12" s="1">
         <v>0</v>
@@ -1660,8 +1657,8 @@
       <c r="J12" s="1">
         <v>0</v>
       </c>
-      <c r="K12" s="3">
-        <v>1</v>
+      <c r="K12" s="1">
+        <v>0.84</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1669,22 +1666,22 @@
         <v>7</v>
       </c>
       <c r="C13" s="1">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="D13" s="1">
-        <v>140</v>
-      </c>
-      <c r="E13" s="3">
-        <v>1.2</v>
-      </c>
-      <c r="F13" s="3">
-        <v>1.8</v>
-      </c>
-      <c r="G13" s="3">
-        <v>1.2</v>
-      </c>
-      <c r="H13" s="3">
-        <v>1.8</v>
+        <v>94</v>
+      </c>
+      <c r="E13" s="1">
+        <v>2.1</v>
+      </c>
+      <c r="F13" s="1">
+        <v>2.8</v>
+      </c>
+      <c r="G13" s="1">
+        <v>2.1</v>
+      </c>
+      <c r="H13" s="1">
+        <v>2.8</v>
       </c>
       <c r="I13" s="1">
         <v>0</v>
@@ -1692,8 +1689,8 @@
       <c r="J13" s="1">
         <v>0</v>
       </c>
-      <c r="K13" s="3">
-        <v>0.8</v>
+      <c r="K13" s="1">
+        <v>0.75</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1701,22 +1698,22 @@
         <v>8</v>
       </c>
       <c r="C14" s="1">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="D14" s="1">
-        <v>120</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="F14" s="3">
-        <v>1.2</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="H14" s="3">
-        <v>1.2</v>
+        <v>75</v>
+      </c>
+      <c r="E14" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="F14" s="1">
+        <v>2.1</v>
+      </c>
+      <c r="G14" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="H14" s="1">
+        <v>2.1</v>
       </c>
       <c r="I14" s="1">
         <v>0</v>
@@ -1724,8 +1721,8 @@
       <c r="J14" s="1">
         <v>0</v>
       </c>
-      <c r="K14" s="3">
-        <v>0.5</v>
+      <c r="K14" s="1">
+        <v>0.66</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1733,22 +1730,22 @@
         <v>9</v>
       </c>
       <c r="C15" s="1">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D15" s="1">
-        <v>80</v>
-      </c>
-      <c r="E15" s="3">
-        <v>0.6</v>
-      </c>
-      <c r="F15" s="3">
-        <v>0.9</v>
-      </c>
-      <c r="G15" s="3">
-        <v>0.6</v>
-      </c>
-      <c r="H15" s="3">
-        <v>0.9</v>
+        <v>60</v>
+      </c>
+      <c r="E15" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="F15" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="G15" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="H15" s="1">
+        <v>1.6</v>
       </c>
       <c r="I15" s="1">
         <v>0</v>
@@ -1756,8 +1753,8 @@
       <c r="J15" s="1">
         <v>0</v>
       </c>
-      <c r="K15" s="3">
-        <v>0.4</v>
+      <c r="K15" s="1">
+        <v>0.61</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1765,22 +1762,22 @@
         <v>10</v>
       </c>
       <c r="C16" s="1">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="D16" s="1">
-        <v>50</v>
-      </c>
-      <c r="E16" s="3">
-        <v>0.4</v>
-      </c>
-      <c r="F16" s="3">
-        <v>0.6</v>
-      </c>
-      <c r="G16" s="3">
-        <v>0.4</v>
-      </c>
-      <c r="H16" s="3">
-        <v>0.6</v>
+        <v>45</v>
+      </c>
+      <c r="E16" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="F16" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="H16" s="1">
+        <v>1.3</v>
       </c>
       <c r="I16" s="1">
         <v>0</v>
@@ -1788,8 +1785,8 @@
       <c r="J16" s="1">
         <v>0</v>
       </c>
-      <c r="K16" s="3">
-        <v>0.25</v>
+      <c r="K16" s="1">
+        <v>0.57</v>
       </c>
     </row>
     <row r="17" spans="2:11">
@@ -1797,22 +1794,22 @@
         <v>11</v>
       </c>
       <c r="C17" s="1">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="D17" s="1">
-        <v>20</v>
-      </c>
-      <c r="E17" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="F17" s="3">
-        <v>0.3</v>
-      </c>
-      <c r="G17" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="H17" s="3">
-        <v>0.3</v>
+        <v>34</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="F17" s="1">
+        <v>1</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="H17" s="1">
+        <v>1</v>
       </c>
       <c r="I17" s="1">
         <v>0</v>
@@ -1820,8 +1817,8 @@
       <c r="J17" s="1">
         <v>0</v>
       </c>
-      <c r="K17" s="3">
-        <v>0.1</v>
+      <c r="K17" s="1">
+        <v>0.54</v>
       </c>
     </row>
     <row r="18" spans="2:11">
@@ -1829,22 +1826,22 @@
         <v>12</v>
       </c>
       <c r="C18" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D18" s="1">
-        <v>7</v>
-      </c>
-      <c r="E18" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="F18" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="G18" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="H18" s="3">
-        <v>0.15</v>
+        <v>23</v>
+      </c>
+      <c r="E18" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="F18" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="H18" s="1">
+        <v>0.9</v>
       </c>
       <c r="I18" s="1">
         <v>0</v>
@@ -1852,8 +1849,8 @@
       <c r="J18" s="1">
         <v>0</v>
       </c>
-      <c r="K18" s="3">
-        <v>0.05</v>
+      <c r="K18" s="1">
+        <v>0.52</v>
       </c>
     </row>
     <row r="19" spans="2:11">
@@ -1864,19 +1861,19 @@
         <v>0</v>
       </c>
       <c r="D19" s="1">
-        <v>0</v>
-      </c>
-      <c r="E19" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="F19" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="G19" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="H19" s="3">
-        <v>0.15</v>
+        <v>11</v>
+      </c>
+      <c r="E19" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="F19" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="H19" s="1">
+        <v>0.7</v>
       </c>
       <c r="I19" s="1">
         <v>0</v>
@@ -1884,8 +1881,8 @@
       <c r="J19" s="1">
         <v>0</v>
       </c>
-      <c r="K19" s="3">
-        <v>0.05</v>
+      <c r="K19" s="1">
+        <v>0.01</v>
       </c>
     </row>
   </sheetData>

--- a/DesignerConfigs/Datas/MoneyInterval.xlsx
+++ b/DesignerConfigs/Datas/MoneyInterval.xlsx
@@ -1285,7 +1285,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K51"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -1460,10 +1460,10 @@
         <v>17.9</v>
       </c>
       <c r="I6" s="1">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J6" s="1">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="K6" s="1">
         <v>2.5</v>
@@ -1492,10 +1492,10 @@
         <v>12.2</v>
       </c>
       <c r="I7" s="1">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J7" s="1">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="K7" s="1">
         <v>1.84</v>
@@ -1524,10 +1524,10 @@
         <v>9.8</v>
       </c>
       <c r="I8" s="1">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J8" s="1">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="K8" s="1">
         <v>1.55</v>
@@ -1556,10 +1556,10 @@
         <v>7.6</v>
       </c>
       <c r="I9" s="1">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J9" s="1">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="K9" s="1">
         <v>1.3</v>
@@ -1588,10 +1588,10 @@
         <v>6.1</v>
       </c>
       <c r="I10" s="1">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J10" s="1">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="K10" s="1">
         <v>1.13</v>
@@ -1620,10 +1620,10 @@
         <v>4.8</v>
       </c>
       <c r="I11" s="1">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J11" s="1">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="K11" s="1">
         <v>0.98</v>
@@ -1652,10 +1652,10 @@
         <v>3.7</v>
       </c>
       <c r="I12" s="1">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="J12" s="1">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K12" s="1">
         <v>0.84</v>
@@ -1684,10 +1684,10 @@
         <v>2.8</v>
       </c>
       <c r="I13" s="1">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="J13" s="1">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K13" s="1">
         <v>0.75</v>
@@ -1716,10 +1716,10 @@
         <v>2.1</v>
       </c>
       <c r="I14" s="1">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="J14" s="1">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="K14" s="1">
         <v>0.66</v>
@@ -1748,10 +1748,10 @@
         <v>1.6</v>
       </c>
       <c r="I15" s="1">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="J15" s="1">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="K15" s="1">
         <v>0.61</v>
@@ -1780,10 +1780,10 @@
         <v>1.3</v>
       </c>
       <c r="I16" s="1">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="J16" s="1">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="K16" s="1">
         <v>0.57</v>
@@ -1812,10 +1812,10 @@
         <v>1</v>
       </c>
       <c r="I17" s="1">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="J17" s="1">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="K17" s="1">
         <v>0.54</v>
@@ -1844,10 +1844,10 @@
         <v>0.9</v>
       </c>
       <c r="I18" s="1">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="J18" s="1">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="K18" s="1">
         <v>0.52</v>
@@ -1876,14 +1876,51 @@
         <v>0.7</v>
       </c>
       <c r="I19" s="1">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="J19" s="1">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="K19" s="1">
         <v>0.01</v>
       </c>
+    </row>
+    <row r="36" ht="12" customHeight="1"/>
+    <row r="49" spans="2:11">
+      <c r="B49"/>
+      <c r="C49"/>
+      <c r="D49"/>
+      <c r="E49"/>
+      <c r="F49"/>
+      <c r="G49"/>
+      <c r="H49"/>
+      <c r="I49"/>
+      <c r="J49"/>
+      <c r="K49"/>
+    </row>
+    <row r="50" spans="2:11">
+      <c r="B50"/>
+      <c r="C50"/>
+      <c r="D50"/>
+      <c r="E50"/>
+      <c r="F50"/>
+      <c r="G50"/>
+      <c r="H50"/>
+      <c r="I50"/>
+      <c r="J50"/>
+      <c r="K50"/>
+    </row>
+    <row r="51" spans="2:11">
+      <c r="B51"/>
+      <c r="C51"/>
+      <c r="D51"/>
+      <c r="E51"/>
+      <c r="F51"/>
+      <c r="G51"/>
+      <c r="H51"/>
+      <c r="I51"/>
+      <c r="J51"/>
+      <c r="K51"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DesignerConfigs/Datas/MoneyInterval.xlsx
+++ b/DesignerConfigs/Datas/MoneyInterval.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="30">
   <si>
     <t>##var</t>
   </si>
@@ -59,6 +59,12 @@
     <t>SEMax</t>
   </si>
   <si>
+    <t>AdBottleMin</t>
+  </si>
+  <si>
+    <t>AdBottleMax</t>
+  </si>
+  <si>
     <t>LSReward</t>
   </si>
   <si>
@@ -102,6 +108,12 @@
   </si>
   <si>
     <t>单次消除最大值</t>
+  </si>
+  <si>
+    <t>广告瓶解锁最小值</t>
+  </si>
+  <si>
+    <t>广告瓶解锁最大值</t>
   </si>
   <si>
     <t>转盘金额</t>
@@ -1285,7 +1297,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K51"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -1295,12 +1307,12 @@
     <col min="7" max="7" width="17.875" style="1" customWidth="1"/>
     <col min="8" max="8" width="17.375" style="1" customWidth="1"/>
     <col min="9" max="9" width="11.375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="16.625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="15.5" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="1"/>
+    <col min="10" max="12" width="16.625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="15.5" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1334,8 +1346,14 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:13">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1349,48 +1367,56 @@
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:13">
       <c r="A3" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:13">
       <c r="A4" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -1401,526 +1427,619 @@
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:13">
       <c r="A5" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:13">
       <c r="B6" s="1">
         <v>0</v>
       </c>
       <c r="C6" s="1">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="D6" s="1">
-        <v>300</v>
+        <v>10000</v>
       </c>
       <c r="E6" s="1">
-        <v>13.3</v>
+        <v>61.4</v>
       </c>
       <c r="F6" s="1">
-        <v>17.9</v>
+        <v>83.07</v>
       </c>
       <c r="G6" s="1">
-        <v>13.3</v>
+        <v>117.8</v>
       </c>
       <c r="H6" s="1">
-        <v>17.9</v>
+        <v>159.3</v>
       </c>
       <c r="I6" s="1">
-        <v>0.2</v>
+        <v>12.49</v>
       </c>
       <c r="J6" s="1">
-        <v>0.2</v>
+        <v>16.9</v>
       </c>
       <c r="K6" s="1">
-        <v>2.5</v>
+        <v>61.4</v>
+      </c>
+      <c r="L6" s="1">
+        <v>83.07</v>
+      </c>
+      <c r="M6" s="1">
+        <v>14.89</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:13">
       <c r="B7" s="1">
         <v>1</v>
       </c>
       <c r="C7" s="1">
-        <v>210</v>
+        <v>800</v>
       </c>
       <c r="D7" s="1">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="E7" s="1">
-        <v>9</v>
+        <v>61.4</v>
       </c>
       <c r="F7" s="1">
-        <v>12.2</v>
+        <v>83.07</v>
       </c>
       <c r="G7" s="1">
-        <v>9</v>
+        <v>117.8</v>
       </c>
       <c r="H7" s="1">
-        <v>12.2</v>
+        <v>159.3</v>
       </c>
       <c r="I7" s="1">
-        <v>0.2</v>
+        <v>12.49</v>
       </c>
       <c r="J7" s="1">
-        <v>0.2</v>
+        <v>16.9</v>
       </c>
       <c r="K7" s="1">
-        <v>1.84</v>
+        <v>61.4</v>
+      </c>
+      <c r="L7" s="1">
+        <v>83.07</v>
+      </c>
+      <c r="M7" s="1">
+        <v>14.89</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:13">
       <c r="B8" s="1">
         <v>2</v>
       </c>
       <c r="C8" s="1">
-        <v>180</v>
+        <v>700</v>
       </c>
       <c r="D8" s="1">
-        <v>210</v>
+        <v>800</v>
       </c>
       <c r="E8" s="1">
-        <v>7.2</v>
+        <v>45.17</v>
       </c>
       <c r="F8" s="1">
-        <v>9.8</v>
+        <v>61.11</v>
       </c>
       <c r="G8" s="1">
-        <v>7.2</v>
+        <v>83.2</v>
       </c>
       <c r="H8" s="1">
-        <v>9.8</v>
+        <v>112.5</v>
       </c>
       <c r="I8" s="1">
-        <v>0.2</v>
+        <v>8.86</v>
       </c>
       <c r="J8" s="1">
-        <v>0.2</v>
+        <v>11.99</v>
       </c>
       <c r="K8" s="1">
-        <v>1.55</v>
+        <v>45.17</v>
+      </c>
+      <c r="L8" s="1">
+        <v>61.11</v>
+      </c>
+      <c r="M8" s="1">
+        <v>10.87</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:13">
       <c r="B9" s="1">
         <v>3</v>
       </c>
       <c r="C9" s="1">
-        <v>158</v>
+        <v>600</v>
       </c>
       <c r="D9" s="1">
-        <v>180</v>
+        <v>700</v>
       </c>
       <c r="E9" s="1">
-        <v>5.6</v>
+        <v>36.06</v>
       </c>
       <c r="F9" s="1">
-        <v>7.6</v>
+        <v>48.79</v>
       </c>
       <c r="G9" s="1">
-        <v>5.6</v>
+        <v>63.7</v>
       </c>
       <c r="H9" s="1">
-        <v>7.6</v>
+        <v>86.2</v>
       </c>
       <c r="I9" s="1">
-        <v>0.1</v>
+        <v>6.83</v>
       </c>
       <c r="J9" s="1">
-        <v>0.2</v>
+        <v>9.23</v>
       </c>
       <c r="K9" s="1">
-        <v>1.3</v>
+        <v>36.06</v>
+      </c>
+      <c r="L9" s="1">
+        <v>48.79</v>
+      </c>
+      <c r="M9" s="1">
+        <v>8.62</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:13">
       <c r="B10" s="1">
         <v>4</v>
       </c>
       <c r="C10" s="1">
-        <v>135</v>
+        <v>525</v>
       </c>
       <c r="D10" s="1">
-        <v>158</v>
+        <v>600</v>
       </c>
       <c r="E10" s="1">
-        <v>4.5</v>
+        <v>29.21</v>
       </c>
       <c r="F10" s="1">
-        <v>6.1</v>
+        <v>39.52</v>
       </c>
       <c r="G10" s="1">
-        <v>4.5</v>
+        <v>49.1</v>
       </c>
       <c r="H10" s="1">
-        <v>6.1</v>
+        <v>66.5</v>
       </c>
       <c r="I10" s="1">
-        <v>0.1</v>
+        <v>5.29</v>
       </c>
       <c r="J10" s="1">
-        <v>0.15</v>
+        <v>7.16</v>
       </c>
       <c r="K10" s="1">
-        <v>1.13</v>
+        <v>29.21</v>
+      </c>
+      <c r="L10" s="1">
+        <v>39.52</v>
+      </c>
+      <c r="M10" s="1">
+        <v>6.92</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:13">
       <c r="B11" s="1">
         <v>5</v>
       </c>
       <c r="C11" s="1">
-        <v>113</v>
+        <v>450</v>
       </c>
       <c r="D11" s="1">
-        <v>135</v>
+        <v>525</v>
       </c>
       <c r="E11" s="1">
-        <v>3.5</v>
+        <v>24.16</v>
       </c>
       <c r="F11" s="1">
-        <v>4.8</v>
+        <v>32.69</v>
       </c>
       <c r="G11" s="1">
-        <v>3.5</v>
+        <v>38.4</v>
       </c>
       <c r="H11" s="1">
-        <v>4.8</v>
+        <v>51.9</v>
       </c>
       <c r="I11" s="1">
-        <v>0.1</v>
+        <v>4.16</v>
       </c>
       <c r="J11" s="1">
-        <v>0.15</v>
+        <v>5.63</v>
       </c>
       <c r="K11" s="1">
-        <v>0.98</v>
+        <v>24.16</v>
+      </c>
+      <c r="L11" s="1">
+        <v>32.69</v>
+      </c>
+      <c r="M11" s="1">
+        <v>5.67</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:13">
       <c r="B12" s="1">
         <v>6</v>
       </c>
       <c r="C12" s="1">
-        <v>94</v>
+        <v>375</v>
       </c>
       <c r="D12" s="1">
-        <v>113</v>
+        <v>450</v>
       </c>
       <c r="E12" s="1">
-        <v>2.7</v>
+        <v>19.87</v>
       </c>
       <c r="F12" s="1">
-        <v>3.7</v>
+        <v>26.88</v>
       </c>
       <c r="G12" s="1">
-        <v>2.7</v>
+        <v>29.2</v>
       </c>
       <c r="H12" s="1">
-        <v>3.7</v>
+        <v>39.5</v>
       </c>
       <c r="I12" s="1">
-        <v>0.05</v>
+        <v>3.2</v>
       </c>
       <c r="J12" s="1">
-        <v>0.1</v>
+        <v>4.33</v>
       </c>
       <c r="K12" s="1">
-        <v>0.84</v>
+        <v>19.87</v>
+      </c>
+      <c r="L12" s="1">
+        <v>26.88</v>
+      </c>
+      <c r="M12" s="1">
+        <v>4.6</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:13">
       <c r="B13" s="1">
         <v>7</v>
       </c>
       <c r="C13" s="1">
-        <v>75</v>
+        <v>313</v>
       </c>
       <c r="D13" s="1">
-        <v>94</v>
+        <v>375</v>
       </c>
       <c r="E13" s="1">
-        <v>2.1</v>
+        <v>16.59</v>
       </c>
       <c r="F13" s="1">
-        <v>2.8</v>
+        <v>22.44</v>
       </c>
       <c r="G13" s="1">
-        <v>2.1</v>
+        <v>22.2</v>
       </c>
       <c r="H13" s="1">
-        <v>2.8</v>
+        <v>30.1</v>
       </c>
       <c r="I13" s="1">
-        <v>0.05</v>
+        <v>2.47</v>
       </c>
       <c r="J13" s="1">
-        <v>0.1</v>
+        <v>3.34</v>
       </c>
       <c r="K13" s="1">
-        <v>0.75</v>
+        <v>16.59</v>
+      </c>
+      <c r="L13" s="1">
+        <v>22.44</v>
+      </c>
+      <c r="M13" s="1">
+        <v>3.79</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:13">
       <c r="B14" s="1">
         <v>8</v>
       </c>
       <c r="C14" s="1">
-        <v>60</v>
+        <v>250</v>
       </c>
       <c r="D14" s="1">
-        <v>75</v>
+        <v>313</v>
       </c>
       <c r="E14" s="1">
-        <v>1.6</v>
+        <v>14.15</v>
       </c>
       <c r="F14" s="1">
-        <v>2.1</v>
+        <v>19.14</v>
       </c>
       <c r="G14" s="1">
-        <v>1.6</v>
+        <v>17</v>
       </c>
       <c r="H14" s="1">
-        <v>2.1</v>
+        <v>23</v>
       </c>
       <c r="I14" s="1">
-        <v>0.05</v>
+        <v>1.92</v>
       </c>
       <c r="J14" s="1">
-        <v>0.08</v>
+        <v>2.6</v>
       </c>
       <c r="K14" s="1">
-        <v>0.66</v>
+        <v>14.15</v>
+      </c>
+      <c r="L14" s="1">
+        <v>19.14</v>
+      </c>
+      <c r="M14" s="1">
+        <v>3.19</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:13">
       <c r="B15" s="1">
         <v>9</v>
       </c>
       <c r="C15" s="1">
-        <v>45</v>
+        <v>200</v>
       </c>
       <c r="D15" s="1">
-        <v>60</v>
+        <v>250</v>
       </c>
       <c r="E15" s="1">
-        <v>1.2</v>
+        <v>12.39</v>
       </c>
       <c r="F15" s="1">
-        <v>1.6</v>
+        <v>16.76</v>
       </c>
       <c r="G15" s="1">
-        <v>1.2</v>
+        <v>13.3</v>
       </c>
       <c r="H15" s="1">
-        <v>1.6</v>
+        <v>18</v>
       </c>
       <c r="I15" s="1">
-        <v>0.04</v>
+        <v>1.53</v>
       </c>
       <c r="J15" s="1">
-        <v>0.06</v>
+        <v>2.07</v>
       </c>
       <c r="K15" s="1">
-        <v>0.61</v>
+        <v>12.39</v>
+      </c>
+      <c r="L15" s="1">
+        <v>16.76</v>
+      </c>
+      <c r="M15" s="1">
+        <v>2.75</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:13">
       <c r="B16" s="1">
         <v>10</v>
       </c>
       <c r="C16" s="1">
-        <v>34</v>
+        <v>150</v>
       </c>
       <c r="D16" s="1">
-        <v>45</v>
+        <v>200</v>
       </c>
       <c r="E16" s="1">
-        <v>0.9</v>
+        <v>11.16</v>
       </c>
       <c r="F16" s="1">
-        <v>1.3</v>
+        <v>15.1</v>
       </c>
       <c r="G16" s="1">
-        <v>0.9</v>
+        <v>10.7</v>
       </c>
       <c r="H16" s="1">
-        <v>1.3</v>
+        <v>14.4</v>
       </c>
       <c r="I16" s="1">
-        <v>0.04</v>
+        <v>1.26</v>
       </c>
       <c r="J16" s="1">
-        <v>0.06</v>
+        <v>1.7</v>
       </c>
       <c r="K16" s="1">
-        <v>0.57</v>
+        <v>11.16</v>
+      </c>
+      <c r="L16" s="1">
+        <v>15.1</v>
+      </c>
+      <c r="M16" s="1">
+        <v>2.45</v>
       </c>
     </row>
-    <row r="17" spans="2:11">
+    <row r="17" spans="2:13">
       <c r="B17" s="1">
         <v>11</v>
       </c>
       <c r="C17" s="1">
-        <v>23</v>
+        <v>113</v>
       </c>
       <c r="D17" s="1">
-        <v>34</v>
+        <v>150</v>
       </c>
       <c r="E17" s="1">
-        <v>0.8</v>
+        <v>11</v>
       </c>
       <c r="F17" s="1">
-        <v>1</v>
+        <v>14.01</v>
       </c>
       <c r="G17" s="1">
-        <v>0.8</v>
+        <v>8.9</v>
       </c>
       <c r="H17" s="1">
-        <v>1</v>
+        <v>12.1</v>
       </c>
       <c r="I17" s="1">
-        <v>0.03</v>
+        <v>1.07</v>
       </c>
       <c r="J17" s="1">
-        <v>0.05</v>
+        <v>1.45</v>
       </c>
       <c r="K17" s="1">
-        <v>0.54</v>
+        <v>11</v>
+      </c>
+      <c r="L17" s="1">
+        <v>14.01</v>
+      </c>
+      <c r="M17" s="1">
+        <v>2.25</v>
       </c>
     </row>
-    <row r="18" spans="2:11">
+    <row r="18" spans="2:13">
       <c r="B18" s="1">
         <v>12</v>
       </c>
       <c r="C18" s="1">
+        <v>75</v>
+      </c>
+      <c r="D18" s="1">
+        <v>113</v>
+      </c>
+      <c r="E18" s="1">
         <v>11</v>
       </c>
-      <c r="D18" s="1">
-        <v>23</v>
-      </c>
-      <c r="E18" s="1">
-        <v>0.6</v>
-      </c>
       <c r="F18" s="1">
-        <v>0.9</v>
+        <v>13.33</v>
       </c>
       <c r="G18" s="1">
-        <v>0.6</v>
+        <v>7.9</v>
       </c>
       <c r="H18" s="1">
-        <v>0.9</v>
+        <v>10.7</v>
       </c>
       <c r="I18" s="1">
-        <v>0.02</v>
+        <v>1</v>
       </c>
       <c r="J18" s="1">
-        <v>0.02</v>
+        <v>1.3</v>
       </c>
       <c r="K18" s="1">
-        <v>0.52</v>
+        <v>11</v>
+      </c>
+      <c r="L18" s="1">
+        <v>13.33</v>
+      </c>
+      <c r="M18" s="1">
+        <v>2.12</v>
       </c>
     </row>
-    <row r="19" spans="2:11">
+    <row r="19" spans="2:13">
       <c r="B19" s="1">
         <v>13</v>
       </c>
       <c r="C19" s="1">
+        <v>38</v>
+      </c>
+      <c r="D19" s="1">
+        <v>75</v>
+      </c>
+      <c r="E19" s="1">
+        <v>11</v>
+      </c>
+      <c r="F19" s="1">
+        <v>12.89</v>
+      </c>
+      <c r="G19" s="1">
+        <v>7.2</v>
+      </c>
+      <c r="H19" s="1">
+        <v>9.7</v>
+      </c>
+      <c r="I19" s="1">
+        <v>1</v>
+      </c>
+      <c r="J19" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="K19" s="1">
+        <v>11</v>
+      </c>
+      <c r="L19" s="1">
+        <v>12.89</v>
+      </c>
+      <c r="M19" s="1">
+        <v>2.04</v>
+      </c>
+    </row>
+    <row r="20" spans="2:13">
+      <c r="B20" s="1">
+        <v>14</v>
+      </c>
+      <c r="C20" s="1">
         <v>0</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D20" s="1">
+        <v>38</v>
+      </c>
+      <c r="E20" s="1">
         <v>11</v>
       </c>
-      <c r="E19" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="F19" s="1">
-        <v>0.7</v>
-      </c>
-      <c r="G19" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="H19" s="1">
-        <v>0.7</v>
-      </c>
-      <c r="I19" s="1">
-        <v>0.02</v>
-      </c>
-      <c r="J19" s="1">
-        <v>0.02</v>
-      </c>
-      <c r="K19" s="1">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="36" ht="12" customHeight="1"/>
-    <row r="49" spans="2:11">
-      <c r="B49"/>
-      <c r="C49"/>
-      <c r="D49"/>
-      <c r="E49"/>
-      <c r="F49"/>
-      <c r="G49"/>
-      <c r="H49"/>
-      <c r="I49"/>
-      <c r="J49"/>
-      <c r="K49"/>
-    </row>
-    <row r="50" spans="2:11">
-      <c r="B50"/>
-      <c r="C50"/>
-      <c r="D50"/>
-      <c r="E50"/>
-      <c r="F50"/>
-      <c r="G50"/>
-      <c r="H50"/>
-      <c r="I50"/>
-      <c r="J50"/>
-      <c r="K50"/>
-    </row>
-    <row r="51" spans="2:11">
-      <c r="B51"/>
-      <c r="C51"/>
-      <c r="D51"/>
-      <c r="E51"/>
-      <c r="F51"/>
-      <c r="G51"/>
-      <c r="H51"/>
-      <c r="I51"/>
-      <c r="J51"/>
-      <c r="K51"/>
+      <c r="F20" s="1">
+        <v>12.68</v>
+      </c>
+      <c r="G20" s="1">
+        <v>6.8</v>
+      </c>
+      <c r="H20" s="1">
+        <v>9.3</v>
+      </c>
+      <c r="I20" s="1">
+        <v>1</v>
+      </c>
+      <c r="J20" s="1">
+        <v>1.16</v>
+      </c>
+      <c r="K20" s="1">
+        <v>11</v>
+      </c>
+      <c r="L20" s="1">
+        <v>12.68</v>
+      </c>
+      <c r="M20" s="1">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DesignerConfigs/Datas/MoneyInterval.xlsx
+++ b/DesignerConfigs/Datas/MoneyInterval.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Level" sheetId="1" r:id="rId1"/>
@@ -1482,22 +1482,22 @@
         <v>10000</v>
       </c>
       <c r="E6" s="1">
-        <v>61.4</v>
+        <v>65</v>
       </c>
       <c r="F6" s="1">
-        <v>83.07</v>
+        <v>120</v>
       </c>
       <c r="G6" s="1">
-        <v>117.8</v>
+        <v>130</v>
       </c>
       <c r="H6" s="1">
-        <v>159.3</v>
+        <v>180</v>
       </c>
       <c r="I6" s="1">
-        <v>12.49</v>
+        <v>15</v>
       </c>
       <c r="J6" s="1">
-        <v>16.9</v>
+        <v>22</v>
       </c>
       <c r="K6" s="1">
         <v>61.4</v>

--- a/DesignerConfigs/Datas/MoneyInterval.xlsx
+++ b/DesignerConfigs/Datas/MoneyInterval.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Level" sheetId="1" r:id="rId1"/>
@@ -742,7 +742,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -750,6 +750,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="22" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1438,451 +1441,579 @@
       </c>
     </row>
     <row r="6" spans="1:11">
-      <c r="B6" s="1">
+      <c r="B6" s="3">
         <v>0</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="3">
+        <v>270</v>
+      </c>
+      <c r="D6" s="3">
+        <v>300</v>
+      </c>
+      <c r="E6" s="3">
+        <v>10</v>
+      </c>
+      <c r="F6" s="3">
+        <v>14</v>
+      </c>
+      <c r="G6" s="3">
+        <v>12</v>
+      </c>
+      <c r="H6" s="3">
+        <v>17</v>
+      </c>
+      <c r="I6" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="J6" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="K6" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="B7" s="3">
+        <v>1</v>
+      </c>
+      <c r="C7" s="3">
         <v>240</v>
       </c>
-      <c r="D6" s="1">
-        <v>300</v>
-      </c>
-      <c r="E6" s="1">
-        <v>13.3</v>
-      </c>
-      <c r="F6" s="1">
-        <v>17.9</v>
-      </c>
-      <c r="G6" s="1">
-        <v>13.3</v>
-      </c>
-      <c r="H6" s="1">
-        <v>17.9</v>
-      </c>
-      <c r="I6" s="1">
+      <c r="D7" s="3">
+        <v>270</v>
+      </c>
+      <c r="E7" s="3">
+        <v>8</v>
+      </c>
+      <c r="F7" s="3">
+        <v>10</v>
+      </c>
+      <c r="G7" s="3">
+        <v>10</v>
+      </c>
+      <c r="H7" s="3">
+        <v>14</v>
+      </c>
+      <c r="I7" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="J7" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="K7" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="B8" s="3">
+        <v>2</v>
+      </c>
+      <c r="C8" s="3">
+        <v>220</v>
+      </c>
+      <c r="D8" s="3">
+        <v>240</v>
+      </c>
+      <c r="E8" s="3">
+        <v>6</v>
+      </c>
+      <c r="F8" s="3">
+        <v>9</v>
+      </c>
+      <c r="G8" s="3">
+        <v>8</v>
+      </c>
+      <c r="H8" s="3">
+        <v>11</v>
+      </c>
+      <c r="I8" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="J8" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="K8" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="B9" s="3">
+        <v>3</v>
+      </c>
+      <c r="C9" s="3">
+        <v>200</v>
+      </c>
+      <c r="D9" s="3">
+        <v>220</v>
+      </c>
+      <c r="E9" s="3">
+        <v>6</v>
+      </c>
+      <c r="F9" s="3">
+        <v>8</v>
+      </c>
+      <c r="G9" s="3">
+        <v>8</v>
+      </c>
+      <c r="H9" s="3">
+        <v>10</v>
+      </c>
+      <c r="I9" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="J9" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="K9" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="B10" s="3">
+        <v>4</v>
+      </c>
+      <c r="C10" s="3">
+        <v>180</v>
+      </c>
+      <c r="D10" s="3">
+        <v>200</v>
+      </c>
+      <c r="E10" s="3">
+        <v>6</v>
+      </c>
+      <c r="F10" s="3">
+        <v>7</v>
+      </c>
+      <c r="G10" s="3">
+        <v>8</v>
+      </c>
+      <c r="H10" s="3">
+        <v>9</v>
+      </c>
+      <c r="I10" s="3">
         <v>0.2</v>
       </c>
-      <c r="J6" s="1">
+      <c r="J10" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="K10" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="B11" s="3">
+        <v>5</v>
+      </c>
+      <c r="C11" s="3">
+        <v>165</v>
+      </c>
+      <c r="D11" s="3">
+        <v>180</v>
+      </c>
+      <c r="E11" s="3">
+        <v>2</v>
+      </c>
+      <c r="F11" s="3">
+        <v>5</v>
+      </c>
+      <c r="G11" s="3">
+        <v>4</v>
+      </c>
+      <c r="H11" s="3">
+        <v>7</v>
+      </c>
+      <c r="I11" s="3">
         <v>0.2</v>
       </c>
-      <c r="K6" s="1">
+      <c r="J11" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="K11" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="B12" s="3">
+        <v>6</v>
+      </c>
+      <c r="C12" s="3">
+        <v>150</v>
+      </c>
+      <c r="D12" s="3">
+        <v>165</v>
+      </c>
+      <c r="E12" s="3">
+        <v>2</v>
+      </c>
+      <c r="F12" s="3">
+        <v>3</v>
+      </c>
+      <c r="G12" s="3">
+        <v>2</v>
+      </c>
+      <c r="H12" s="3">
+        <v>4</v>
+      </c>
+      <c r="I12" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="J12" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="K12" s="3">
         <v>2.5</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
-      <c r="B7" s="1">
+    <row r="13" spans="1:11">
+      <c r="B13" s="3">
+        <v>7</v>
+      </c>
+      <c r="C13" s="3">
+        <v>137</v>
+      </c>
+      <c r="D13" s="3">
+        <v>150</v>
+      </c>
+      <c r="E13" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="F13" s="3">
+        <v>2</v>
+      </c>
+      <c r="G13" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="H13" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="I13" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="J13" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="K13" s="3">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="B14" s="3">
+        <v>8</v>
+      </c>
+      <c r="C14" s="3">
+        <v>125</v>
+      </c>
+      <c r="D14" s="3">
+        <v>137</v>
+      </c>
+      <c r="E14" s="3">
         <v>1</v>
       </c>
-      <c r="C7" s="1">
-        <v>210</v>
-      </c>
-      <c r="D7" s="1">
-        <v>240</v>
-      </c>
-      <c r="E7" s="1">
+      <c r="F14" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="G14" s="3">
+        <v>1.3</v>
+      </c>
+      <c r="H14" s="3">
+        <v>2</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="B15" s="3">
         <v>9</v>
       </c>
-      <c r="F7" s="1">
-        <v>12.2</v>
-      </c>
-      <c r="G7" s="1">
-        <v>9</v>
-      </c>
-      <c r="H7" s="1">
-        <v>12.2</v>
-      </c>
-      <c r="I7" s="1">
+      <c r="C15" s="3">
+        <v>110</v>
+      </c>
+      <c r="D15" s="3">
+        <v>125</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="F15" s="3">
+        <v>1.4</v>
+      </c>
+      <c r="G15" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="H15" s="3">
+        <v>1.8</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="J15" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="K15" s="3">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="B16" s="3">
+        <v>10</v>
+      </c>
+      <c r="C16" s="3">
+        <v>95</v>
+      </c>
+      <c r="D16" s="3">
+        <v>110</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="F16" s="3">
+        <v>1</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="H16" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="I16" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="J16" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="K16" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11">
+      <c r="B17" s="3">
+        <v>11</v>
+      </c>
+      <c r="C17" s="3">
+        <v>75</v>
+      </c>
+      <c r="D17" s="3">
+        <v>95</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="H17" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="I17" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="J17" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="K17" s="3">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11">
+      <c r="B18" s="3">
+        <v>12</v>
+      </c>
+      <c r="C18" s="3">
+        <v>60</v>
+      </c>
+      <c r="D18" s="3">
+        <v>75</v>
+      </c>
+      <c r="E18" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="F18" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="G18" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="H18" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="I18" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="J18" s="3">
+        <v>0.08</v>
+      </c>
+      <c r="K18" s="3">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11">
+      <c r="B19" s="3">
+        <v>13</v>
+      </c>
+      <c r="C19" s="3">
+        <v>45</v>
+      </c>
+      <c r="D19" s="3">
+        <v>60</v>
+      </c>
+      <c r="E19" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="F19" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="G19" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="H19" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="I19" s="3">
+        <v>0.04</v>
+      </c>
+      <c r="J19" s="3">
+        <v>0.06</v>
+      </c>
+      <c r="K19" s="3">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11">
+      <c r="B20" s="3">
+        <v>14</v>
+      </c>
+      <c r="C20" s="3">
+        <v>35</v>
+      </c>
+      <c r="D20" s="3">
+        <v>45</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0.04</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0.06</v>
+      </c>
+      <c r="K20" s="3">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11">
+      <c r="B21" s="3">
+        <v>15</v>
+      </c>
+      <c r="C21" s="3">
+        <v>23</v>
+      </c>
+      <c r="D21" s="3">
+        <v>35</v>
+      </c>
+      <c r="E21" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="F21" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="G21" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="H21" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="I21" s="3">
+        <v>0.03</v>
+      </c>
+      <c r="J21" s="3">
+        <v>0.04</v>
+      </c>
+      <c r="K21" s="3">
         <v>0.2</v>
       </c>
-      <c r="J7" s="1">
+    </row>
+    <row r="22" spans="2:11">
+      <c r="B22" s="3">
+        <v>16</v>
+      </c>
+      <c r="C22" s="3">
+        <v>11</v>
+      </c>
+      <c r="D22" s="3">
+        <v>23</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="F22" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="G22" s="3">
         <v>0.2</v>
       </c>
-      <c r="K7" s="1">
-        <v>1.84</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="B8" s="1">
-        <v>2</v>
-      </c>
-      <c r="C8" s="1">
-        <v>180</v>
-      </c>
-      <c r="D8" s="1">
-        <v>210</v>
-      </c>
-      <c r="E8" s="1">
-        <v>7.2</v>
-      </c>
-      <c r="F8" s="1">
-        <v>9.8</v>
-      </c>
-      <c r="G8" s="1">
-        <v>7.2</v>
-      </c>
-      <c r="H8" s="1">
-        <v>9.8</v>
-      </c>
-      <c r="I8" s="1">
+      <c r="H22" s="3">
         <v>0.2</v>
       </c>
-      <c r="J8" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="K8" s="1">
-        <v>1.55</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="B9" s="1">
-        <v>3</v>
-      </c>
-      <c r="C9" s="1">
-        <v>158</v>
-      </c>
-      <c r="D9" s="1">
-        <v>180</v>
-      </c>
-      <c r="E9" s="1">
-        <v>5.6</v>
-      </c>
-      <c r="F9" s="1">
-        <v>7.6</v>
-      </c>
-      <c r="G9" s="1">
-        <v>5.6</v>
-      </c>
-      <c r="H9" s="1">
-        <v>7.6</v>
-      </c>
-      <c r="I9" s="1">
+      <c r="I22" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="K22" s="3">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="23" spans="2:11">
+      <c r="B23" s="3">
+        <v>17</v>
+      </c>
+      <c r="C23" s="3">
+        <v>0</v>
+      </c>
+      <c r="D23" s="3">
+        <v>11</v>
+      </c>
+      <c r="E23" s="3">
         <v>0.1</v>
       </c>
-      <c r="J9" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="K9" s="1">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="B10" s="1">
-        <v>4</v>
-      </c>
-      <c r="C10" s="1">
-        <v>135</v>
-      </c>
-      <c r="D10" s="1">
-        <v>158</v>
-      </c>
-      <c r="E10" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="F10" s="1">
-        <v>6.1</v>
-      </c>
-      <c r="G10" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="H10" s="1">
-        <v>6.1</v>
-      </c>
-      <c r="I10" s="1">
+      <c r="F23" s="3">
         <v>0.1</v>
       </c>
-      <c r="J10" s="1">
-        <v>0.15</v>
-      </c>
-      <c r="K10" s="1">
-        <v>1.13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="B11" s="1">
-        <v>5</v>
-      </c>
-      <c r="C11" s="1">
-        <v>113</v>
-      </c>
-      <c r="D11" s="1">
-        <v>135</v>
-      </c>
-      <c r="E11" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="F11" s="1">
-        <v>4.8</v>
-      </c>
-      <c r="G11" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="H11" s="1">
-        <v>4.8</v>
-      </c>
-      <c r="I11" s="1">
+      <c r="G23" s="3">
         <v>0.1</v>
       </c>
-      <c r="J11" s="1">
-        <v>0.15</v>
-      </c>
-      <c r="K11" s="1">
-        <v>0.98</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="B12" s="1">
-        <v>6</v>
-      </c>
-      <c r="C12" s="1">
-        <v>94</v>
-      </c>
-      <c r="D12" s="1">
-        <v>113</v>
-      </c>
-      <c r="E12" s="1">
-        <v>2.7</v>
-      </c>
-      <c r="F12" s="1">
-        <v>3.7</v>
-      </c>
-      <c r="G12" s="1">
-        <v>2.7</v>
-      </c>
-      <c r="H12" s="1">
-        <v>3.7</v>
-      </c>
-      <c r="I12" s="1">
-        <v>0.05</v>
-      </c>
-      <c r="J12" s="1">
+      <c r="H23" s="3">
         <v>0.1</v>
       </c>
-      <c r="K12" s="1">
-        <v>0.84</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="B13" s="1">
-        <v>7</v>
-      </c>
-      <c r="C13" s="1">
-        <v>75</v>
-      </c>
-      <c r="D13" s="1">
-        <v>94</v>
-      </c>
-      <c r="E13" s="1">
-        <v>2.1</v>
-      </c>
-      <c r="F13" s="1">
-        <v>2.8</v>
-      </c>
-      <c r="G13" s="1">
-        <v>2.1</v>
-      </c>
-      <c r="H13" s="1">
-        <v>2.8</v>
-      </c>
-      <c r="I13" s="1">
-        <v>0.05</v>
-      </c>
-      <c r="J13" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="K13" s="1">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="B14" s="1">
-        <v>8</v>
-      </c>
-      <c r="C14" s="1">
-        <v>60</v>
-      </c>
-      <c r="D14" s="1">
-        <v>75</v>
-      </c>
-      <c r="E14" s="1">
-        <v>1.6</v>
-      </c>
-      <c r="F14" s="1">
-        <v>2.1</v>
-      </c>
-      <c r="G14" s="1">
-        <v>1.6</v>
-      </c>
-      <c r="H14" s="1">
-        <v>2.1</v>
-      </c>
-      <c r="I14" s="1">
-        <v>0.05</v>
-      </c>
-      <c r="J14" s="1">
-        <v>0.08</v>
-      </c>
-      <c r="K14" s="1">
-        <v>0.66</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="B15" s="1">
-        <v>9</v>
-      </c>
-      <c r="C15" s="1">
-        <v>45</v>
-      </c>
-      <c r="D15" s="1">
-        <v>60</v>
-      </c>
-      <c r="E15" s="1">
-        <v>1.2</v>
-      </c>
-      <c r="F15" s="1">
-        <v>1.6</v>
-      </c>
-      <c r="G15" s="1">
-        <v>1.2</v>
-      </c>
-      <c r="H15" s="1">
-        <v>1.6</v>
-      </c>
-      <c r="I15" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="J15" s="1">
-        <v>0.06</v>
-      </c>
-      <c r="K15" s="1">
-        <v>0.61</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="B16" s="1">
-        <v>10</v>
-      </c>
-      <c r="C16" s="1">
-        <v>34</v>
-      </c>
-      <c r="D16" s="1">
-        <v>45</v>
-      </c>
-      <c r="E16" s="1">
-        <v>0.9</v>
-      </c>
-      <c r="F16" s="1">
-        <v>1.3</v>
-      </c>
-      <c r="G16" s="1">
-        <v>0.9</v>
-      </c>
-      <c r="H16" s="1">
-        <v>1.3</v>
-      </c>
-      <c r="I16" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="J16" s="1">
-        <v>0.06</v>
-      </c>
-      <c r="K16" s="1">
-        <v>0.57</v>
-      </c>
-    </row>
-    <row r="17" spans="2:11">
-      <c r="B17" s="1">
-        <v>11</v>
-      </c>
-      <c r="C17" s="1">
-        <v>23</v>
-      </c>
-      <c r="D17" s="1">
-        <v>34</v>
-      </c>
-      <c r="E17" s="1">
-        <v>0.8</v>
-      </c>
-      <c r="F17" s="1">
-        <v>1</v>
-      </c>
-      <c r="G17" s="1">
-        <v>0.8</v>
-      </c>
-      <c r="H17" s="1">
-        <v>1</v>
-      </c>
-      <c r="I17" s="1">
-        <v>0.03</v>
-      </c>
-      <c r="J17" s="1">
-        <v>0.05</v>
-      </c>
-      <c r="K17" s="1">
-        <v>0.54</v>
-      </c>
-    </row>
-    <row r="18" spans="2:11">
-      <c r="B18" s="1">
-        <v>12</v>
-      </c>
-      <c r="C18" s="1">
-        <v>11</v>
-      </c>
-      <c r="D18" s="1">
-        <v>23</v>
-      </c>
-      <c r="E18" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="F18" s="1">
-        <v>0.9</v>
-      </c>
-      <c r="G18" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="H18" s="1">
-        <v>0.9</v>
-      </c>
-      <c r="I18" s="1">
+      <c r="I23" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="J23" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="K23" s="3">
         <v>0.02</v>
-      </c>
-      <c r="J18" s="1">
-        <v>0.02</v>
-      </c>
-      <c r="K18" s="1">
-        <v>0.52</v>
-      </c>
-    </row>
-    <row r="19" spans="2:11">
-      <c r="B19" s="1">
-        <v>13</v>
-      </c>
-      <c r="C19" s="1">
-        <v>0</v>
-      </c>
-      <c r="D19" s="1">
-        <v>11</v>
-      </c>
-      <c r="E19" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="F19" s="1">
-        <v>0.7</v>
-      </c>
-      <c r="G19" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="H19" s="1">
-        <v>0.7</v>
-      </c>
-      <c r="I19" s="1">
-        <v>0.02</v>
-      </c>
-      <c r="J19" s="1">
-        <v>0.02</v>
-      </c>
-      <c r="K19" s="1">
-        <v>0.01</v>
       </c>
     </row>
     <row r="36" ht="12" customHeight="1"/>

--- a/DesignerConfigs/Datas/MoneyInterval.xlsx
+++ b/DesignerConfigs/Datas/MoneyInterval.xlsx
@@ -1646,7 +1646,7 @@
         <v>2</v>
       </c>
       <c r="F12" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G12" s="3">
         <v>2</v>
@@ -1742,13 +1742,13 @@
         <v>0.8</v>
       </c>
       <c r="F15" s="3">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="G15" s="3">
         <v>1.2</v>
       </c>
       <c r="H15" s="3">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="I15" s="3">
         <v>0.1</v>
@@ -1925,7 +1925,7 @@
         <v>15</v>
       </c>
       <c r="C21" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D21" s="3">
         <v>35</v>
@@ -1960,7 +1960,7 @@
         <v>11</v>
       </c>
       <c r="D22" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E22" s="3">
         <v>0.1</v>
@@ -1972,7 +1972,7 @@
         <v>0.2</v>
       </c>
       <c r="H22" s="3">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="I22" s="3">
         <v>0.02</v>
@@ -1989,22 +1989,22 @@
         <v>17</v>
       </c>
       <c r="C23" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D23" s="3">
         <v>11</v>
       </c>
       <c r="E23" s="3">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="F23" s="3">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="G23" s="3">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="H23" s="3">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="I23" s="3">
         <v>0.01</v>
@@ -2014,6 +2014,38 @@
       </c>
       <c r="K23" s="3">
         <v>0.02</v>
+      </c>
+    </row>
+    <row r="24" spans="2:11">
+      <c r="B24" s="3">
+        <v>18</v>
+      </c>
+      <c r="C24" s="1">
+        <v>0</v>
+      </c>
+      <c r="D24" s="1">
+        <v>5</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="H24" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="I24" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="J24" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="K24" s="1">
+        <v>0.01</v>
       </c>
     </row>
     <row r="36" ht="12" customHeight="1"/>
